--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488264_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488264_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>R. GUERRA ZAYAS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9157</v>
+        <v>7.0746</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0998</v>
+        <v>10.7205</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.184</v>
+        <v>-3.6459</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3218</v>
+        <v>7.6614</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8115</v>
+        <v>9.907</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.4897</v>
+        <v>-2.2456</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2948</v>
+        <v>11.0279</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4654</v>
+        <v>10.9544</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8294</v>
+        <v>0.0735</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.9729</v>
+        <v>-3.3665</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6538</v>
+        <v>-1.0474</v>
       </c>
       <c r="O2" t="n">
         <v>-2.3191</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4823</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9083</v>
+        <v>0.859</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2137</v>
+        <v>0.2882</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6946</v>
+        <v>0.5708</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2033</v>
+        <v>-1.2605</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5177</v>
+        <v>1.2572</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3144</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. GUERRA ZAYAS</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4618</v>
+        <v>5.8368</v>
       </c>
       <c r="E3" t="n">
-        <v>10.2308</v>
+        <v>7.3163</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.769</v>
+        <v>-1.4795</v>
       </c>
       <c r="G3" t="n">
-        <v>7.6614</v>
+        <v>1.3218</v>
       </c>
       <c r="H3" t="n">
-        <v>9.907</v>
+        <v>2.8115</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.2456</v>
+        <v>-1.4897</v>
       </c>
       <c r="J3" t="n">
-        <v>11.0279</v>
+        <v>5.2948</v>
       </c>
       <c r="K3" t="n">
-        <v>10.9544</v>
+        <v>4.4654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0735</v>
+        <v>0.8294</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3665</v>
+        <v>-3.9729</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0474</v>
+        <v>-1.6538</v>
       </c>
       <c r="O3" t="n">
         <v>-2.3191</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2462</v>
+        <v>0.8294</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2014</v>
+        <v>0.4303</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4476</v>
+        <v>0.3991</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2605</v>
+        <v>2.2033</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2572</v>
+        <v>2.5177</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.5177</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>R. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2662</v>
+        <v>1.5278</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2662</v>
+        <v>0.8619</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2662</v>
+        <v>1.7148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6441</v>
+        <v>1.1095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6221</v>
+        <v>0.6052</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2662</v>
+        <v>1.9208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6441</v>
+        <v>1.8378</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6221</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.206</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.5223</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.1275</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.1324</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.2599</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. ORTEGA MORA</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2088</v>
+        <v>1.2662</v>
       </c>
       <c r="E5" t="n">
-        <v>0.666</v>
+        <v>1.2662</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5427999999999999</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7148</v>
+        <v>1.2662</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1095</v>
+        <v>0.6441</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6052</v>
+        <v>0.6221</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9208</v>
+        <v>1.2662</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8378</v>
+        <v>0.6441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0829</v>
+        <v>0.6221</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.206</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7282999999999999</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5223</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1915</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3283</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1368</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VALDERRAMA VIDAL</t>
+          <t>J. LOPEZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8406</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7644</v>
+        <v>1.0719</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.893</v>
+        <v>-0.2313</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8936</v>
+        <v>-0.7138</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4206</v>
+        <v>0.3645</v>
       </c>
       <c r="I6" t="n">
-        <v>0.473</v>
+        <v>-1.0783</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1346</v>
+        <v>2.2845</v>
       </c>
       <c r="K6" t="n">
-        <v>2.439</v>
+        <v>1.5889</v>
       </c>
       <c r="L6" t="n">
         <v>0.6956</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.241</v>
+        <v>-2.9982</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0184</v>
+        <v>-1.2244</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2226</v>
+        <v>-1.7738</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2234</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>1.107</v>
+        <v>0.8126</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.3439</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3273</v>
+        <v>0.4688</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5733</v>
+        <v>0.0005</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.2027</v>
+        <v>0.6304999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. RUESGA MORALES</t>
+          <t>A. VALDERRAMA VIDAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0193</v>
+        <v>0.2581</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6019</v>
+        <v>1.3727</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.5826</v>
+        <v>-1.1146</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0705</v>
+        <v>1.8936</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1778</v>
+        <v>1.4206</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1072</v>
+        <v>0.473</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7676</v>
+        <v>3.1346</v>
       </c>
       <c r="K7" t="n">
-        <v>4.0104</v>
+        <v>2.439</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7572</v>
+        <v>0.6956</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.6971</v>
+        <v>-1.241</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8327</v>
+        <v>-1.0184</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.8644</v>
+        <v>-0.2226</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.297</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4823</v>
+        <v>2.2234</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5613</v>
+        <v>0.4937</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6703</v>
+        <v>0.388</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.109</v>
+        <v>0.1057</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3155</v>
+        <v>-1.5733</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9433</v>
+        <v>0.6294</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. LLANO ABASCAL</t>
+          <t>F. RUESGA MORALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0799</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2009</v>
+        <v>3.504</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2807</v>
+        <v>-3.4103</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5256</v>
+        <v>1.0705</v>
       </c>
       <c r="H8" t="n">
-        <v>0.542</v>
+        <v>3.1778</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0676</v>
+        <v>-2.1072</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2878</v>
+        <v>4.7676</v>
       </c>
       <c r="K8" t="n">
-        <v>0.365</v>
+        <v>4.0104</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6529</v>
+        <v>0.7572</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2377</v>
+        <v>-3.6971</v>
       </c>
       <c r="N8" t="n">
-        <v>0.177</v>
+        <v>-0.8327</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4147</v>
+        <v>-2.8644</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4457</v>
+        <v>0.6358</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4887</v>
+        <v>0.5724</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.043</v>
+        <v>0.0634</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. LOPEZ RUIZ</t>
+          <t>I. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4834</v>
+        <v>-0.4223</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0926</v>
+        <v>-0.1908</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.576</v>
+        <v>-0.2315</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7138</v>
+        <v>-0.5256</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3645</v>
+        <v>0.542</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0783</v>
+        <v>-1.0676</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2845</v>
+        <v>-0.2878</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5889</v>
+        <v>0.365</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6956</v>
+        <v>-0.6529</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9982</v>
+        <v>-0.2377</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2244</v>
+        <v>0.177</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7738</v>
+        <v>-0.4147</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5113</v>
+        <v>0.1032</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6354</v>
+        <v>0.097</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1241</v>
+        <v>0.0062</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6304999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. JIMENEZ HERRERA</t>
+          <t>E. NGOM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9673</v>
+        <v>-1.4473</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9563</v>
+        <v>-1.0287</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9236</v>
+        <v>-0.4186</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3752</v>
+        <v>-1.0655</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0517</v>
+        <v>-0.8873</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4269</v>
+        <v>-0.1782</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6088</v>
+        <v>-1.1584</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8931</v>
+        <v>-0.5884</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7157</v>
+        <v>-0.5699</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.984</v>
+        <v>0.0929</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8414</v>
+        <v>-0.2989</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.1426</v>
+        <v>0.3917</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4087</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8723</v>
+        <v>0.3211</v>
       </c>
       <c r="T10" t="n">
-        <v>0.868</v>
+        <v>0.1296</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0043</v>
+        <v>0.1915</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9444</v>
+        <v>-1.2589</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. NGOM</t>
+          <t>D. JIMENEZ HERRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7904</v>
+        <v>-1.7775</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3225</v>
+        <v>0.5646</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4679</v>
+        <v>-2.3421</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0655</v>
+        <v>-1.3752</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8873</v>
+        <v>0.0517</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1782</v>
+        <v>-1.4269</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1584</v>
+        <v>1.6088</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5884</v>
+        <v>0.8931</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5699</v>
+        <v>0.7157</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0929</v>
+        <v>-2.984</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2989</v>
+        <v>-0.8414</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3917</v>
+        <v>-2.1426</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0219</v>
+        <v>1.062</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1641</v>
+        <v>0.4763</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1423</v>
+        <v>0.5857</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2589</v>
+        <v>0.9444</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.435</v>
+        <v>-2.2632</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7247</v>
+        <v>-0.6267</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7103</v>
+        <v>-1.6364</v>
       </c>
       <c r="G12" t="n">
         <v>0.5517</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.616</v>
+        <v>-0.4443</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2878</v>
+        <v>-0.2139</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.9873</v>
+        <v>10.9875</v>
       </c>
       <c r="E13" t="n">
-        <v>24.8317</v>
+        <v>24.8319</v>
       </c>
       <c r="F13" t="n">
         <v>-13.8443</v>
@@ -1459,7 +1459,7 @@
         <v>-11.7106</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.779300000000001</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.8229</v>
@@ -1468,7 +1468,7 @@
         <v>12.0436</v>
       </c>
       <c r="S13" t="n">
-        <v>4.800100000000001</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>2.3629</v>
@@ -1483,7 +1483,7 @@
         <v>5.9765</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.809799999999999</v>
+        <v>-8.809800000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5171</v>
+        <v>4.604</v>
       </c>
       <c r="E14" t="n">
-        <v>8.531499999999999</v>
+        <v>9.217000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.0144</v>
+        <v>-4.613</v>
       </c>
       <c r="G14" t="n">
         <v>4.1454</v>
@@ -1546,13 +1546,13 @@
         <v>2.4087</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.11</v>
+        <v>-1.0231</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2584</v>
+        <v>-0.5729</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8516</v>
+        <v>-0.4502</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0005</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9645</v>
+        <v>2.5064</v>
       </c>
       <c r="E15" t="n">
-        <v>8.367100000000001</v>
+        <v>7.9754</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.4025</v>
+        <v>-5.4689</v>
       </c>
       <c r="G15" t="n">
         <v>-2.5327</v>
@@ -1624,13 +1624,13 @@
         <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4793</v>
+        <v>0.0211</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5609</v>
+        <v>0.1691</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.148</v>
       </c>
       <c r="V15" t="n">
         <v>4.0915</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>M. CASERO MIGLIAVACCA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.116</v>
+        <v>-0.3957</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.189</v>
+        <v>4.4017</v>
       </c>
       <c r="F16" t="n">
-        <v>0.305</v>
+        <v>-4.7974</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3406</v>
+        <v>-0.6727</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5911</v>
+        <v>-3.1853</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2505</v>
+        <v>2.5125</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3796</v>
+        <v>4.8248</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5455</v>
+        <v>1.5674</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1659</v>
+        <v>3.2574</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.961</v>
+        <v>-5.4975</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.0455</v>
+        <v>-4.7527</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.7448</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2157</v>
+        <v>-0.8347</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5061</v>
+        <v>-0.4405</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7095</v>
+        <v>-0.3942</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3155</v>
+        <v>0.9439</v>
       </c>
       <c r="X16" t="n">
-        <v>0.63</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CASERO MIGLIAVACCA</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1637</v>
+        <v>-0.8902</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9121</v>
+        <v>-0.7766</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.0757</v>
+        <v>-0.1136</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6727</v>
+        <v>-2.3406</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.1853</v>
+        <v>-2.5911</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5125</v>
+        <v>0.2505</v>
       </c>
       <c r="J17" t="n">
-        <v>4.8248</v>
+        <v>-0.3796</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5674</v>
+        <v>-0.5455</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2574</v>
+        <v>0.1659</v>
       </c>
       <c r="M17" t="n">
-        <v>-5.4975</v>
+        <v>-1.961</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.7527</v>
+        <v>-2.0455</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7448</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6027</v>
+        <v>0.2095</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9302</v>
+        <v>-0.0814</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6725</v>
+        <v>0.291</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9439</v>
+        <v>-0.3155</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9439</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7536</v>
+        <v>-1.3859</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4705</v>
+        <v>-1.1767</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.283</v>
+        <v>-0.2092</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2489</v>
@@ -1858,13 +1858,13 @@
         <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7466</v>
+        <v>-0.379</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4166</v>
+        <v>-0.1228</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.33</v>
+        <v>-0.2562</v>
       </c>
       <c r="V18" t="n">
         <v>0.3155</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4618</v>
+        <v>-2.2677</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1801</v>
+        <v>1.0856</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.2818</v>
+        <v>-3.3533</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9929</v>
+        <v>0.5793</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8163</v>
+        <v>-1.6893</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1766</v>
+        <v>2.2686</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1074</v>
+        <v>4.7422</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1074</v>
+        <v>1.8593</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.8829</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1003</v>
+        <v>-4.1628</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9237</v>
+        <v>-3.5485</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1766</v>
+        <v>-0.6143</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7411</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7411</v>
+        <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8951</v>
+        <v>-0.4209</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6019</v>
+        <v>0.0491</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2932</v>
+        <v>-0.4701</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.315</v>
+        <v>-0.9439</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6294</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9389</v>
+        <v>-2.3141</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8897</v>
+        <v>-0.1801</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8286</v>
+        <v>-2.134</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5793</v>
+        <v>-1.9929</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6893</v>
+        <v>-1.8163</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2686</v>
+        <v>-0.1766</v>
       </c>
       <c r="J20" t="n">
-        <v>4.7422</v>
+        <v>0.1074</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8593</v>
+        <v>0.1074</v>
       </c>
       <c r="L20" t="n">
-        <v>2.8829</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.1628</v>
+        <v>-2.1003</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.5485</v>
+        <v>-1.9237</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6143</v>
+        <v>-0.1766</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0921</v>
+        <v>-0.7474</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1467</v>
+        <v>-0.6019</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9453</v>
+        <v>-0.1455</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9439</v>
+        <v>-0.315</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9439</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.158</v>
+        <v>-4.3058</v>
       </c>
       <c r="E21" t="n">
         <v>-2.0159</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1422</v>
+        <v>-2.2899</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1478</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3808</v>
+        <v>-0.5285</v>
       </c>
       <c r="T21" t="n">
         <v>-0.5807</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1999</v>
+        <v>0.0522</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2589</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.109</v>
+        <v>-5.8855</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0005</v>
+        <v>-4.686</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1086</v>
+        <v>-1.1996</v>
       </c>
       <c r="G22" t="n">
         <v>-4.589</v>
@@ -2170,13 +2170,13 @@
         <v>2.2234</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3323</v>
+        <v>-0.4443</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4303</v>
+        <v>-0.2552</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.098</v>
+        <v>-0.189</v>
       </c>
       <c r="V22" t="n">
         <v>0.63</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.9874</v>
+        <v>-10.3345</v>
       </c>
       <c r="E23" t="n">
         <v>13.8444</v>
       </c>
       <c r="F23" t="n">
-        <v>-24.8318</v>
+        <v>-24.1789</v>
       </c>
       <c r="G23" t="n">
         <v>-11.7999</v>
@@ -2248,13 +2248,13 @@
         <v>14.8228</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.8</v>
+        <v>-4.1473</v>
       </c>
       <c r="T23" t="n">
         <v>-2.4372</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.3628</v>
+        <v>-1.71</v>
       </c>
       <c r="V23" t="n">
         <v>2.8331</v>
